--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0003T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0003T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.56309122584219</v>
+        <v>7.241502324199357</v>
       </c>
       <c r="D2" t="n">
-        <v>15.38862904530932</v>
+        <v>2.500652219862765</v>
       </c>
       <c r="E2" t="n">
-        <v>9.20103510086232</v>
+        <v>1.495168203890127</v>
       </c>
       <c r="F2" t="n">
-        <v>14.04272563472662</v>
+        <v>2.281942915643075</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>62.96516142756683</v>
+        <v>10.23183873197961</v>
       </c>
       <c r="D3" t="n">
-        <v>43.47408031476255</v>
+        <v>7.064538051148915</v>
       </c>
       <c r="E3" t="n">
-        <v>9.20103510086232</v>
+        <v>1.495168203890127</v>
       </c>
       <c r="F3" t="n">
-        <v>14.04272563472662</v>
+        <v>2.281942915643075</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
